--- a/docs/planning/Jyotish_DE_Backlog_v3.xlsx
+++ b/docs/planning/Jyotish_DE_Backlog_v3.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Epics" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User Stories" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Plan" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tech Launch Checklist" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vendors &amp; Costs" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team &amp; Effort" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Epics" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="User Stories" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Release Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Tech Launch Checklist" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Vendors &amp; Costs" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Team &amp; Effort" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'User Stories'!$A$1:$M$114</definedName>
@@ -645,9 +645,6 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-    </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2103,7 +2100,7 @@
       <c r="K2" s="7" t="inlineStr"/>
       <c r="L2" s="9" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="M2" s="9" t="inlineStr"/>
@@ -2197,7 +2194,7 @@
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>1) All compute, DB, storage and backups in eu-central-1 (Frankfurt). 2) No production data in dev or staging. 3) Secrets in a managed store, never in the repo. 4) Defined in IaC and reproducible.</t>
+          <t>1) All compute, DB, storage and backups in eu-central-1 (Frankfurt). 2) No production data in dev or staging. 3) Secrets in a managed store, never in the repo. 4) Defined in IaC and reproducible. DESCOPED (2026-08-01): single environment only for now (Hetzner, fsn1), pre-launch/pre-real-users — see infra/README.md. Full dev/staging/prod split must land before real users or payments go live.</t>
         </is>
       </c>
       <c r="G4" s="14" t="inlineStr">
@@ -2225,7 +2222,7 @@
       </c>
       <c r="L4" s="9" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="M4" s="9" t="inlineStr"/>

--- a/docs/planning/Jyotish_DE_Backlog_v3.xlsx
+++ b/docs/planning/Jyotish_DE_Backlog_v3.xlsx
@@ -2255,7 +2255,7 @@
       </c>
       <c r="F5" s="11" t="inlineStr">
         <is>
-          <t>1) Tokens for colour, type, spacing, radii and elevation. 2) 20+ core components. 3) Light and dark themes. 4) Accessibility: 4.5:1 contrast minimum, 44pt tap targets.</t>
+          <t>1) Tokens for colour, type, spacing, radii and elevation. 2) 20+ core components. 3) Light and dark themes. 4) Accessibility: 4.5:1 contrast minimum, 44pt tap targets. VERIFIED (2026-08-02): 28 components; contrast recomputed from the WCAG spec in test/design/contrast_test.dart (41 assertions, both themes); 44pt targets asserted per component incl. at 2x text scale. KNOWN DEBT: five German accessibility strings are hardcoded pending l10n (epic E09) — see the note in core/design/design_system.dart.</t>
         </is>
       </c>
       <c r="G5" s="17" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="L5" s="9" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="M5" s="9" t="inlineStr"/>

--- a/docs/planning/Jyotish_DE_Backlog_v3.xlsx
+++ b/docs/planning/Jyotish_DE_Backlog_v3.xlsx
@@ -6647,7 +6647,7 @@
       </c>
       <c r="F77" s="11" t="inlineStr">
         <is>
-          <t>1) No hardcoded strings; ICU format with plurals. 2) German date DD.MM.YYYY, 24-hour time, comma decimals, EUR 11,00 formatting. 3) Device locale with in-app override. 4) Pseudo-localisation test for overflow - German runs about 30% longer.</t>
+          <t>1) No hardcoded strings; ICU format with plurals. 2) German date DD.MM.YYYY, 24-hour time, comma decimals, EUR 11,00 formatting. 3) Device locale with in-app override. 4) Pseudo-localisation test for overflow - German runs about 30% longer. VERIFIED (2026-08-02): de-DE template + en-GB translation, ICU plurals, in-app override persisted via shared_preferences, pseudo-localisation at 1.3x/2x/3x string length (which caught a real AppKeyValueRow overflow). NOT DONE: US-089 translation-management workflow — ARB files are edited by hand and there is no CI check that a new key reaches the translator.</t>
         </is>
       </c>
       <c r="G77" s="17" t="inlineStr">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="L77" s="9" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="M77" s="9" t="inlineStr"/>

--- a/docs/planning/Jyotish_DE_Backlog_v3.xlsx
+++ b/docs/planning/Jyotish_DE_Backlog_v3.xlsx
@@ -2316,7 +2316,7 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>1) Bottom tabs: Home, Kundali, Karriere, Auswertung, Profil. 2) Deep links resolve correctly. 3) Offline banner; cached chart viewable without network. 4) Cold start under 2.5s on mid-range Android.</t>
+          <t>1) Bottom tabs: Home, Kundali, Karriere, Auswertung, Profil. 2) Deep links resolve correctly. 3) Offline banner; cached chart viewable without network. 4) Cold start under 2.5s on mid-range Android. PARTIAL (2026-08-02). AC1 done: five tabs, state preserved per tab. AC2 done: routes tested and verified on device; a custom-scheme link was broken (host vs path) and is fixed. https App Links declared but cannot verify without the jyotish.de domain and a release signing key. AC3 HALF: offline banner works; "cached chart viewable without network" is not built — no chart exists to cache (needs E03 + the engine). AC4 NOT VERIFIED: release APK on an Android emulator cold-starts 2.19-2.47s, worst 2.63s under host load — at the 2.5s budget, not under it, and an emulator is not a mid-range device. Needs measuring on real hardware.</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="L6" s="9" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="M6" s="9" t="inlineStr"/>

--- a/docs/planning/Jyotish_DE_Backlog_v3.xlsx
+++ b/docs/planning/Jyotish_DE_Backlog_v3.xlsx
@@ -2377,7 +2377,7 @@
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>1) Flags evaluated per user and segment at runtime. 2) Kill switch on the paid evaluation flow. 3) All flag changes audited.</t>
+          <t>1) Flags evaluated per user and segment at runtime. 2) Kill switch on the paid evaluation flow. 3) All flag changes audited. PARTIAL (2026-08-02). AC1 engine done: segments (locale, platform, version range, user list, internal) and deterministic FNV-1a rollout bucketing, per flag so users are not in the same bucket for every rollout; 47 tests. CAVEAT: flagUserIdProvider is still a constant, so every device buckets identically — must be wired to real identity (E02) before any percentage rollout. AC2 done: paid_evaluation kill switch gates the Auswertung flow, cached so it survives restart and network loss; verified in widget tests. AC3 PARTIAL: FlagAuditService refuses any change without actor and reason, append-only, 12 tests — but storage is in-memory because the API has no database, and there is no admin UI or endpoint to change a flag. NO TRANSPORT: nothing serves the document and nothing fetches it, so flags are compiled-in defaults in practice until the API exists.</t>
         </is>
       </c>
       <c r="G7" s="19" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="L7" s="9" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="M7" s="9" t="inlineStr"/>

--- a/docs/planning/Jyotish_DE_Backlog_v3.xlsx
+++ b/docs/planning/Jyotish_DE_Backlog_v3.xlsx
@@ -2438,7 +2438,7 @@
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>1) Structured logs with correlation IDs across app, API and workers. 2) Dashboards for latency, error rate and queue depth. 3) Alerts on p99 over 2s, 5xx over 1%, payment failures. 4) No PII or birth data in logs.</t>
+          <t>1) Structured logs with correlation IDs across app, API and workers. 2) Dashboards for latency, error rate and queue depth. 3) Alerts on p99 over 2s, 5xx over 1%, payment failures. 4) No PII or birth data in logs. PARTIAL (2026-08-02). AC4 DONE: allowlist-based redaction plus pattern scrubbing (email, IBAN, card, coordinates, birth dates, phone, token, IP) in both app and API, 48 tests including a full birth-data payload thrown at the logger. AC1 HALF: structured JSON loggers with correlation-ID propagation exist on both sides (AsyncLocalStorage in the API, Zone in the app), but there is no HTTP layer and no workers, so cross-service propagation is unexercised. AC2/AC3 DEFINED NOT DEPLOYED: alerts.yaml and dashboard.json encode the AC3 thresholds (p99 2s, 5xx 1%, payment failures) and CI fails if they are loosened, but there is no Grafana/Prometheus and the API emits no metrics, so every series referenced is absent and no alert can fire. A deadman rule (JyotishMetricsAbsent) is included precisely because silent non-firing is the failure mode here.</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="L8" s="9" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="M8" s="9" t="inlineStr"/>

--- a/docs/planning/Jyotish_DE_Backlog_v3.xlsx
+++ b/docs/planning/Jyotish_DE_Backlog_v3.xlsx
@@ -2499,7 +2499,7 @@
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>1) Crash-free session rate tracked per release. 2) Symbolicated stack traces. 3) Alert below 99.0%. 4) Consent-gated in the EU.</t>
+          <t>1) Crash-free session rate tracked per release. 2) Symbolicated stack traces. 3) Alert below 99.0%. 4) Consent-gated in the EU. PARTIAL (2026-08-02). AC4 DONE: consent gate with per-category states, only "granted" permits transmission, pre-decision crashes buffered in memory and discarded on refusal, withdrawal takes effect immediately; reports redacted via US-007. Fixed a restore race that could re-grant consent a user had just refused. AC1 DONE locally: per-release session counters, unclean-exit detection verified on device — but nothing transmits the rate. AC2 PARTIAL: scripts/build_release.sh produces obfuscation symbols and refuses to return a build without them (verified, 3 ABIs), but there is no crash service to upload to, so nothing is actually symbolicated. AC3 DEFINED NOT DEPLOYED: JyotishCrashFreeRate alert with a 50-session guard, pinned by CI. BLOCKED ON: no crash reporting account (CrashTransport has only a recording implementation) and no CMP (US-095), so consent is never granted and nothing would send even if a transport existed.</t>
         </is>
       </c>
       <c r="G9" s="17" t="inlineStr">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="L9" s="9" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="M9" s="9" t="inlineStr"/>

--- a/docs/planning/Jyotish_DE_Backlog_v3.xlsx
+++ b/docs/planning/Jyotish_DE_Backlog_v3.xlsx
@@ -2560,7 +2560,7 @@
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>1) Maximum four screens, skippable. 2) German by default when the device locale is de. 3) Explains the free chart, the free career feature and the EUR 11 expert report. 4) Shown once, tracked as onboarding_completed.</t>
+          <t>1) Maximum four screens, skippable. 2) German by default when the device locale is de. 3) Explains the free chart, the free career feature and the EUR 11 expert report. 4) Shown once, tracked as onboarding_completed. VERIFIED (2026-08-02): four pages (asserted, not conventional), skip on every page including the last, both skip and finish record completion. German by default on a de device, en-GB otherwise, price locale-formatted. Free chart, free career (personal-use framing per adr/0005) and the paid report each explained. onboarding_completed persisted under that exact key. 23 tests plus device verification: first run shows it, relaunch after completing goes straight to Home. A deep link arriving on a first run is preserved and resumed rather than swallowed.</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="L10" s="9" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="M10" s="9" t="inlineStr"/>

--- a/docs/planning/Jyotish_DE_Backlog_v3.xlsx
+++ b/docs/planning/Jyotish_DE_Backlog_v3.xlsx
@@ -2499,7 +2499,7 @@
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>1) Crash-free session rate tracked per release. 2) Symbolicated stack traces. 3) Alert below 99.0%. 4) Consent-gated in the EU.</t>
+          <t>1) Crash-free session rate tracked per release. 2) Symbolicated stack traces. 3) Alert below 99.0%. 4) Consent-gated in the EU. PARTIAL (2026-08-02). AC4 DONE: consent gate, only "granted" permits transmission, pre-decision crashes buffered in memory and discarded on refusal, withdrawal immediate; reports redacted via US-007. Fixed a restore race that could re-grant consent a user had just refused. AC1 DONE locally: per-release session counters, unclean-exit detection verified on device; nothing transmits the rate. AC2 PARTIAL: scripts/build_release.sh produces obfuscation symbols and refuses a build without them (3 ABIs), but no crash service exists to upload to. AC3 DEFINED NOT DEPLOYED: JyotishCrashFreeRate with a 50-session guard, pinned by CI. BLOCKED ON: no crash reporting account and no CMP (US-095), so consent is never granted and nothing would send.</t>
         </is>
       </c>
       <c r="G9" s="17" t="inlineStr">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="L9" s="9" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="M9" s="9" t="inlineStr"/>

--- a/docs/planning/Jyotish_DE_Backlog_v3.xlsx
+++ b/docs/planning/Jyotish_DE_Backlog_v3.xlsx
@@ -2621,7 +2621,7 @@
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>1) Email verification link. 2) Password minimum 10 characters with a breach-list check. 3) Rate limiting and lockout after 10 failed attempts. 4) Password reset token valid 30 minutes.</t>
+          <t>1) Email verification link. 2) Password minimum 10 characters with a breach-list check. 3) Rate limiting and lockout after 10 failed attempts. 4) Password reset token valid 30 minutes. PARTIAL (2026-08-06). Domain core in api/src/modules/identity, 121 tests. AC1 DONE at domain level: verification link hashed at rest, single use, 24h; resending replaces the previous link; an unverified account may sign in but the principal carries emailVerified=false for the order module to enforce on. AC2 DONE: minimum ten CODE POINTS (String.length would pass five emoji as ten); breach list queried by five-character SHA-1 prefix so k-anonymity is structural rather than a convention, local list by default so no processor is involved, rejects by default when the list cannot answer; NIST SP 800-63B rules only, no composition requirements. AC3 DONE: ten failures in a 15-minute window locks the account for 15 minutes and the lock expires on its own; separate, much larger per-client budget catches stuffing spread across many addresses; failures counted for addresses with NO account, so lockout is not an enumeration oracle. AC4 DONE: 30-minute single-use reset token, hashed at rest, requesting a new one kills the old, a weak new password is refused without burning the link, and a completed reset revokes sessions, lifts the lockout and verifies the address. Enumeration treated as a requirement throughout: a taken address answers like a fresh one and still pays for a password hash so a stopwatch cannot separate the branches; a login against a missing account still spends a full scrypt verification. NO TRANSPORT: main.ts is still a stub, so there are no HTTP routes and nothing is reachable. NO PERSISTENCE: accounts, tokens and throttle counters are in-memory placeholders -- the throttle must move to Redis (per-instance counters multiply the effective limit by the instance count) and markConsumed must become a conditional update on consumed_at IS NULL or one reset link can be redeemed twice. NO MAILER: the notification module does not exist, so nothing is sent. Sessions are US-016 (SessionRevoker seam already called); social sign-in US-012 (passwordHash is nullable for it). ADR-0006 records the scrypt and breach-list decisions.</t>
         </is>
       </c>
       <c r="G11" s="17" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="L11" s="9" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="M11" s="9" t="inlineStr"/>

--- a/docs/planning/Jyotish_DE_Backlog_v3.xlsx
+++ b/docs/planning/Jyotish_DE_Backlog_v3.xlsx
@@ -2682,7 +2682,7 @@
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>1) Sign in with Apple mandatory on iOS if any social login is offered. 2) Google Sign-In on Android. 3) Account linking on matching email. 4) Apple private-relay addresses handled.</t>
+          <t>1) Sign in with Apple mandatory on iOS if any social login is offered. 2) Google Sign-In on Android. 3) Account linking on matching email. 4) Apple private-relay addresses handled. PARTIAL (2026-08-06). Mobile side in app/lib/features/auth, 71 tests. AC1 DONE: Guideline 4.8 is a function rather than a convention -- providersFor puts Apple first on iOS and returns NOTHING AT ALL when Apple is unavailable there, so a kill switch cannot leave Google alone on an iPhone; asserted over every subset of providers, not just the ones a screen happens to produce. AC2 DONE: Google on Android; Apple deliberately not offered there (possible via a web flow, not required, and a browser hand-off is worse than the native sheet). AC3 DONE client-side: linking turns on the provider's own email_verified assertion. An unverified match yields proof-of-control with NO link button rendered at all, because drawing it and relying on the API to refuse it puts a takeover one bug away. The address in the prompt is masked by the API, so this flow does not reopen the enumeration hole US-011 closed. The rule is a pure function here; the API is the authority and must apply it against the verified identity token, never a client field. AC4 DONE: relay detection matches the whole domain after the @ (a contains check also matches privaterelay.appleid.com.attacker.de); Apple's first-authorisation-only disclosure is written to disk BEFORE the network is touched and replayed onto later credentials, and a null never overwrites a stored value -- the failure this prevents is Apple returning the address, the request timing out, and the retry carrying nothing; the user is told once that a hidden address means the report can become undeliverable if they switch forwarding off. NO SDK: sign_in_with_apple and google_sign_in are not added -- there is no Apple capability, no Services ID and no OAuth client IDs to configure -- so UnconfiguredSocialSignIn reports every provider unavailable and the screen falls back to email and password. NO ENDPOINT: the API has no HTTP layer, so UnavailableAuthGateway ships. Apple's own button asset and approved label styling still required before review. Server-side linking and relay handling are a follow-up on the identity module.</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="L12" s="9" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="M12" s="9" t="inlineStr"/>
